--- a/templates/ERC000024/metadata_template_ERC000024.xlsx
+++ b/templates/ERC000024/metadata_template_ERC000024.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
     <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AQ$1:$AQ$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$85</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="874">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="876">
   <si>
     <t>alias</t>
   </si>
@@ -561,6 +561,9 @@
     <t>DNBSEQ-G50</t>
   </si>
   <si>
+    <t>DNBSEQ-G800</t>
+  </si>
+  <si>
     <t>DNBSEQ-T10x4RS</t>
   </si>
   <si>
@@ -724,6 +727,9 @@
   </si>
   <si>
     <t>UG 100</t>
+  </si>
+  <si>
+    <t>Vega</t>
   </si>
   <si>
     <t>instrument_model</t>
@@ -3188,7 +3194,7 @@
         <v>143</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3232,7 +3238,7 @@
         <v>144</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -3259,7 +3265,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N85"/>
+  <dimension ref="G1:N87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3978,6 +3984,16 @@
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="86" spans="14:14">
+      <c r="N86" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="87" spans="14:14">
+      <c r="N87" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3999,27 +4015,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4039,122 +4055,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -4178,828 +4194,828 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="DP1" s="1" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="DQ1" s="1" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="DR1" s="1" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="DS1" s="1" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="DU1" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="DV1" s="1" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="DW1" s="1" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
     </row>
     <row r="2" spans="1:138" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="DN2" s="2" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="DO2" s="2" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="DP2" s="2" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="DQ2" s="2" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="DR2" s="2" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="DS2" s="2" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="DT2" s="2" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="DU2" s="2" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="DV2" s="2" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="DW2" s="2" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="DX2" s="2" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="DY2" s="2" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="DZ2" s="2" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="EA2" s="2" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="EB2" s="2" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="EC2" s="2" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="ED2" s="2" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="EE2" s="2" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="EF2" s="2" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="EG2" s="2" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="EH2" s="2" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
     </row>
   </sheetData>
@@ -5037,1594 +5053,1594 @@
   <sheetData>
     <row r="1" spans="5:57">
       <c r="E1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="P1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Z1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AQ1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="BE1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="2" spans="5:57">
       <c r="E2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="H2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="P2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Z2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AQ2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="BE2" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="3" spans="5:57">
       <c r="E3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Z3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AQ3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4" spans="5:57">
       <c r="E4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="H4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AQ4" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="5" spans="5:57">
       <c r="E5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="H5" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AQ5" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="6" spans="5:57">
       <c r="E6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AQ6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="7" spans="5:57">
       <c r="E7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H7" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AQ7" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="8" spans="5:57">
       <c r="E8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AQ8" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9" spans="5:57">
       <c r="E9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AQ9" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="10" spans="5:57">
       <c r="E10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AQ10" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="11" spans="5:57">
       <c r="E11" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AQ11" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="12" spans="5:57">
       <c r="E12" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AQ12" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="13" spans="5:57">
       <c r="E13" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AQ13" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="14" spans="5:57">
       <c r="E14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AQ14" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="15" spans="5:57">
       <c r="E15" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AQ15" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="16" spans="5:57">
       <c r="E16" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AQ16" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="17" spans="5:43">
       <c r="E17" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AQ17" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="18" spans="5:43">
       <c r="E18" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AQ18" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="19" spans="5:43">
       <c r="E19" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AQ19" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="20" spans="5:43">
       <c r="E20" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AQ20" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="21" spans="5:43">
       <c r="E21" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AQ21" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="22" spans="5:43">
       <c r="E22" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AQ22" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="23" spans="5:43">
       <c r="E23" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AQ23" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="24" spans="5:43">
       <c r="E24" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AQ24" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="25" spans="5:43">
       <c r="E25" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AQ25" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="26" spans="5:43">
       <c r="E26" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AQ26" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="27" spans="5:43">
       <c r="E27" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AQ27" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="28" spans="5:43">
       <c r="E28" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AQ28" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="29" spans="5:43">
       <c r="E29" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AQ29" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="30" spans="5:43">
       <c r="E30" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AQ30" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="31" spans="5:43">
       <c r="AQ31" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="32" spans="5:43">
       <c r="AQ32" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="33" spans="43:43">
       <c r="AQ33" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="34" spans="43:43">
       <c r="AQ34" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="35" spans="43:43">
       <c r="AQ35" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="36" spans="43:43">
       <c r="AQ36" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="37" spans="43:43">
       <c r="AQ37" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="38" spans="43:43">
       <c r="AQ38" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="39" spans="43:43">
       <c r="AQ39" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="40" spans="43:43">
       <c r="AQ40" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="41" spans="43:43">
       <c r="AQ41" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="42" spans="43:43">
       <c r="AQ42" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="43" spans="43:43">
       <c r="AQ43" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="44" spans="43:43">
       <c r="AQ44" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="45" spans="43:43">
       <c r="AQ45" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="46" spans="43:43">
       <c r="AQ46" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="47" spans="43:43">
       <c r="AQ47" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="48" spans="43:43">
       <c r="AQ48" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="49" spans="43:43">
       <c r="AQ49" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="50" spans="43:43">
       <c r="AQ50" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="51" spans="43:43">
       <c r="AQ51" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="52" spans="43:43">
       <c r="AQ52" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="53" spans="43:43">
       <c r="AQ53" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="54" spans="43:43">
       <c r="AQ54" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="55" spans="43:43">
       <c r="AQ55" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="56" spans="43:43">
       <c r="AQ56" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="57" spans="43:43">
       <c r="AQ57" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="58" spans="43:43">
       <c r="AQ58" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="59" spans="43:43">
       <c r="AQ59" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="60" spans="43:43">
       <c r="AQ60" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="61" spans="43:43">
       <c r="AQ61" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="62" spans="43:43">
       <c r="AQ62" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="63" spans="43:43">
       <c r="AQ63" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="64" spans="43:43">
       <c r="AQ64" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="65" spans="43:43">
       <c r="AQ65" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="66" spans="43:43">
       <c r="AQ66" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="67" spans="43:43">
       <c r="AQ67" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="68" spans="43:43">
       <c r="AQ68" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="69" spans="43:43">
       <c r="AQ69" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="70" spans="43:43">
       <c r="AQ70" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="71" spans="43:43">
       <c r="AQ71" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="72" spans="43:43">
       <c r="AQ72" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="73" spans="43:43">
       <c r="AQ73" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="74" spans="43:43">
       <c r="AQ74" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="75" spans="43:43">
       <c r="AQ75" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="76" spans="43:43">
       <c r="AQ76" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="77" spans="43:43">
       <c r="AQ77" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="78" spans="43:43">
       <c r="AQ78" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="79" spans="43:43">
       <c r="AQ79" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="80" spans="43:43">
       <c r="AQ80" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="81" spans="43:43">
       <c r="AQ81" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="82" spans="43:43">
       <c r="AQ82" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="83" spans="43:43">
       <c r="AQ83" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="84" spans="43:43">
       <c r="AQ84" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="85" spans="43:43">
       <c r="AQ85" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="86" spans="43:43">
       <c r="AQ86" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="87" spans="43:43">
       <c r="AQ87" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="88" spans="43:43">
       <c r="AQ88" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="89" spans="43:43">
       <c r="AQ89" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="90" spans="43:43">
       <c r="AQ90" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="91" spans="43:43">
       <c r="AQ91" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="92" spans="43:43">
       <c r="AQ92" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="93" spans="43:43">
       <c r="AQ93" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="94" spans="43:43">
       <c r="AQ94" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="95" spans="43:43">
       <c r="AQ95" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="96" spans="43:43">
       <c r="AQ96" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="97" spans="43:43">
       <c r="AQ97" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="98" spans="43:43">
       <c r="AQ98" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="99" spans="43:43">
       <c r="AQ99" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="100" spans="43:43">
       <c r="AQ100" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="101" spans="43:43">
       <c r="AQ101" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="102" spans="43:43">
       <c r="AQ102" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="103" spans="43:43">
       <c r="AQ103" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="104" spans="43:43">
       <c r="AQ104" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="105" spans="43:43">
       <c r="AQ105" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="106" spans="43:43">
       <c r="AQ106" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="107" spans="43:43">
       <c r="AQ107" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="108" spans="43:43">
       <c r="AQ108" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="109" spans="43:43">
       <c r="AQ109" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="110" spans="43:43">
       <c r="AQ110" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="111" spans="43:43">
       <c r="AQ111" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="112" spans="43:43">
       <c r="AQ112" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="113" spans="43:43">
       <c r="AQ113" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="114" spans="43:43">
       <c r="AQ114" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="115" spans="43:43">
       <c r="AQ115" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="116" spans="43:43">
       <c r="AQ116" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="117" spans="43:43">
       <c r="AQ117" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="118" spans="43:43">
       <c r="AQ118" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="119" spans="43:43">
       <c r="AQ119" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="120" spans="43:43">
       <c r="AQ120" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="121" spans="43:43">
       <c r="AQ121" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="122" spans="43:43">
       <c r="AQ122" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="123" spans="43:43">
       <c r="AQ123" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="124" spans="43:43">
       <c r="AQ124" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="125" spans="43:43">
       <c r="AQ125" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="126" spans="43:43">
       <c r="AQ126" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="127" spans="43:43">
       <c r="AQ127" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="128" spans="43:43">
       <c r="AQ128" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="129" spans="43:43">
       <c r="AQ129" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="130" spans="43:43">
       <c r="AQ130" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="131" spans="43:43">
       <c r="AQ131" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="132" spans="43:43">
       <c r="AQ132" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="133" spans="43:43">
       <c r="AQ133" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="134" spans="43:43">
       <c r="AQ134" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="135" spans="43:43">
       <c r="AQ135" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="136" spans="43:43">
       <c r="AQ136" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="137" spans="43:43">
       <c r="AQ137" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="138" spans="43:43">
       <c r="AQ138" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="139" spans="43:43">
       <c r="AQ139" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="140" spans="43:43">
       <c r="AQ140" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="141" spans="43:43">
       <c r="AQ141" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="142" spans="43:43">
       <c r="AQ142" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="143" spans="43:43">
       <c r="AQ143" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="144" spans="43:43">
       <c r="AQ144" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="145" spans="43:43">
       <c r="AQ145" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="146" spans="43:43">
       <c r="AQ146" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="147" spans="43:43">
       <c r="AQ147" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="148" spans="43:43">
       <c r="AQ148" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="149" spans="43:43">
       <c r="AQ149" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="150" spans="43:43">
       <c r="AQ150" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="151" spans="43:43">
       <c r="AQ151" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="152" spans="43:43">
       <c r="AQ152" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="153" spans="43:43">
       <c r="AQ153" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="154" spans="43:43">
       <c r="AQ154" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="155" spans="43:43">
       <c r="AQ155" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="156" spans="43:43">
       <c r="AQ156" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="157" spans="43:43">
       <c r="AQ157" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="158" spans="43:43">
       <c r="AQ158" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="159" spans="43:43">
       <c r="AQ159" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="160" spans="43:43">
       <c r="AQ160" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="161" spans="43:43">
       <c r="AQ161" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="162" spans="43:43">
       <c r="AQ162" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="163" spans="43:43">
       <c r="AQ163" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="164" spans="43:43">
       <c r="AQ164" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="165" spans="43:43">
       <c r="AQ165" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="166" spans="43:43">
       <c r="AQ166" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="167" spans="43:43">
       <c r="AQ167" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="168" spans="43:43">
       <c r="AQ168" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="169" spans="43:43">
       <c r="AQ169" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="170" spans="43:43">
       <c r="AQ170" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="171" spans="43:43">
       <c r="AQ171" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="172" spans="43:43">
       <c r="AQ172" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="173" spans="43:43">
       <c r="AQ173" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="174" spans="43:43">
       <c r="AQ174" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="175" spans="43:43">
       <c r="AQ175" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="176" spans="43:43">
       <c r="AQ176" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="177" spans="43:43">
       <c r="AQ177" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="178" spans="43:43">
       <c r="AQ178" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="179" spans="43:43">
       <c r="AQ179" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="180" spans="43:43">
       <c r="AQ180" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="181" spans="43:43">
       <c r="AQ181" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="182" spans="43:43">
       <c r="AQ182" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="183" spans="43:43">
       <c r="AQ183" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="184" spans="43:43">
       <c r="AQ184" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="185" spans="43:43">
       <c r="AQ185" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="186" spans="43:43">
       <c r="AQ186" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="187" spans="43:43">
       <c r="AQ187" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="188" spans="43:43">
       <c r="AQ188" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="189" spans="43:43">
       <c r="AQ189" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="190" spans="43:43">
       <c r="AQ190" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="191" spans="43:43">
       <c r="AQ191" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="192" spans="43:43">
       <c r="AQ192" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="193" spans="43:43">
       <c r="AQ193" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="194" spans="43:43">
       <c r="AQ194" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="195" spans="43:43">
       <c r="AQ195" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="196" spans="43:43">
       <c r="AQ196" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="197" spans="43:43">
       <c r="AQ197" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="198" spans="43:43">
       <c r="AQ198" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="199" spans="43:43">
       <c r="AQ199" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="200" spans="43:43">
       <c r="AQ200" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="201" spans="43:43">
       <c r="AQ201" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="202" spans="43:43">
       <c r="AQ202" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="203" spans="43:43">
       <c r="AQ203" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="204" spans="43:43">
       <c r="AQ204" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="205" spans="43:43">
       <c r="AQ205" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="206" spans="43:43">
       <c r="AQ206" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="207" spans="43:43">
       <c r="AQ207" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="208" spans="43:43">
       <c r="AQ208" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="209" spans="43:43">
       <c r="AQ209" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="210" spans="43:43">
       <c r="AQ210" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="211" spans="43:43">
       <c r="AQ211" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="212" spans="43:43">
       <c r="AQ212" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="213" spans="43:43">
       <c r="AQ213" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="214" spans="43:43">
       <c r="AQ214" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="215" spans="43:43">
       <c r="AQ215" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="216" spans="43:43">
       <c r="AQ216" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="217" spans="43:43">
       <c r="AQ217" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="218" spans="43:43">
       <c r="AQ218" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="219" spans="43:43">
       <c r="AQ219" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="220" spans="43:43">
       <c r="AQ220" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="221" spans="43:43">
       <c r="AQ221" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="222" spans="43:43">
       <c r="AQ222" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="223" spans="43:43">
       <c r="AQ223" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="224" spans="43:43">
       <c r="AQ224" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="225" spans="43:43">
       <c r="AQ225" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="226" spans="43:43">
       <c r="AQ226" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="227" spans="43:43">
       <c r="AQ227" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="228" spans="43:43">
       <c r="AQ228" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="229" spans="43:43">
       <c r="AQ229" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="230" spans="43:43">
       <c r="AQ230" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="231" spans="43:43">
       <c r="AQ231" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="232" spans="43:43">
       <c r="AQ232" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="233" spans="43:43">
       <c r="AQ233" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="234" spans="43:43">
       <c r="AQ234" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="235" spans="43:43">
       <c r="AQ235" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="236" spans="43:43">
       <c r="AQ236" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="237" spans="43:43">
       <c r="AQ237" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="238" spans="43:43">
       <c r="AQ238" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="239" spans="43:43">
       <c r="AQ239" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="240" spans="43:43">
       <c r="AQ240" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="241" spans="43:43">
       <c r="AQ241" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="242" spans="43:43">
       <c r="AQ242" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="243" spans="43:43">
       <c r="AQ243" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="244" spans="43:43">
       <c r="AQ244" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="245" spans="43:43">
       <c r="AQ245" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="246" spans="43:43">
       <c r="AQ246" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="247" spans="43:43">
       <c r="AQ247" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="248" spans="43:43">
       <c r="AQ248" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="249" spans="43:43">
       <c r="AQ249" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="250" spans="43:43">
       <c r="AQ250" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="251" spans="43:43">
       <c r="AQ251" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="252" spans="43:43">
       <c r="AQ252" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="253" spans="43:43">
       <c r="AQ253" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="254" spans="43:43">
       <c r="AQ254" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="255" spans="43:43">
       <c r="AQ255" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="256" spans="43:43">
       <c r="AQ256" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="257" spans="43:43">
       <c r="AQ257" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="258" spans="43:43">
       <c r="AQ258" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="259" spans="43:43">
       <c r="AQ259" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="260" spans="43:43">
       <c r="AQ260" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="261" spans="43:43">
       <c r="AQ261" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="262" spans="43:43">
       <c r="AQ262" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="263" spans="43:43">
       <c r="AQ263" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="264" spans="43:43">
       <c r="AQ264" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="265" spans="43:43">
       <c r="AQ265" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="266" spans="43:43">
       <c r="AQ266" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="267" spans="43:43">
       <c r="AQ267" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="268" spans="43:43">
       <c r="AQ268" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="269" spans="43:43">
       <c r="AQ269" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="270" spans="43:43">
       <c r="AQ270" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="271" spans="43:43">
       <c r="AQ271" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="272" spans="43:43">
       <c r="AQ272" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="273" spans="43:43">
       <c r="AQ273" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="274" spans="43:43">
       <c r="AQ274" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="275" spans="43:43">
       <c r="AQ275" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="276" spans="43:43">
       <c r="AQ276" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="277" spans="43:43">
       <c r="AQ277" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="278" spans="43:43">
       <c r="AQ278" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="279" spans="43:43">
       <c r="AQ279" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="280" spans="43:43">
       <c r="AQ280" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="281" spans="43:43">
       <c r="AQ281" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="282" spans="43:43">
       <c r="AQ282" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="283" spans="43:43">
       <c r="AQ283" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="284" spans="43:43">
       <c r="AQ284" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="285" spans="43:43">
       <c r="AQ285" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="286" spans="43:43">
       <c r="AQ286" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="287" spans="43:43">
       <c r="AQ287" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="288" spans="43:43">
       <c r="AQ288" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="289" spans="43:43">
       <c r="AQ289" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000024/metadata_template_ERC000024.xlsx
+++ b/templates/ERC000024/metadata_template_ERC000024.xlsx
@@ -18,8 +18,8 @@
   </sheets>
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AQ$1:$AQ$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$86</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AQ$1:$AQ$294</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="881">
   <si>
     <t>alias</t>
   </si>
@@ -561,6 +561,9 @@
     <t>DNBSEQ-G50</t>
   </si>
   <si>
+    <t>DNBSEQ-G800</t>
+  </si>
+  <si>
     <t>DNBSEQ-T10x4RS</t>
   </si>
   <si>
@@ -936,7 +939,7 @@
     <t>phototroph</t>
   </si>
   <si>
-    <t>trophic level</t>
+    <t>trophic_level</t>
   </si>
   <si>
     <t>(Optional) Trophic levels are the feeding position in a food chain. microbes can be a range of producers (e.g. chemolithotroph)</t>
@@ -957,13 +960,13 @@
     <t>symbiont</t>
   </si>
   <si>
-    <t>observed biotic relationship</t>
+    <t>observed_biotic_relationship</t>
   </si>
   <si>
     <t>(Optional) Description of relationship(s) between the subject organism and other organism(s) it is associated with. e.g., parasite on species x; mutualist with species y. the target organism is the subject of the relationship, and the other organism(s) is the object.</t>
   </si>
   <si>
-    <t>known pathogenicity</t>
+    <t>known_pathogenicity</t>
   </si>
   <si>
     <t>(Optional) To what is the entity pathogenic, for instance plant, fungi, bacteria</t>
@@ -990,7 +993,7 @@
     <t>obligate anaerobe</t>
   </si>
   <si>
-    <t>relationship to oxygen</t>
+    <t>relationship_to_oxygen</t>
   </si>
   <si>
     <t>(Optional) Is this organism an aerobe, anaerobe? please note that aerobic and anaerobic are valid descriptors for microbial environments</t>
@@ -1002,40 +1005,40 @@
     <t>(Optional) The type of reproduction from the parent stock. values for this field is specific to different taxa. for phage or virus: lytic/lysogenic/temperate/obligately lytic. for plasmids: incompatibility group. for eukaryotes: sexual/asexual. mandatory for migs of eukayotes, plasmids and viruses.</t>
   </si>
   <si>
-    <t>sample collection device</t>
+    <t>sample_collection_device</t>
   </si>
   <si>
     <t>(Optional) The device used to collect an environmental sample. it is recommended to use terms listed under environmental sampling device (http://purl.obolibrary.org/obo/envo) and/or terms listed under specimen collection device (http://purl.obolibrary.org/obo/genepio_0002094).</t>
   </si>
   <si>
-    <t>sample collection method</t>
+    <t>sample_collection_method</t>
   </si>
   <si>
     <t>(Optional) The method employed for collecting the sample. can be provided in the form of a pmid, doi, url or text.</t>
   </si>
   <si>
-    <t>sample storage temperature</t>
+    <t>sample_storage_temperature</t>
   </si>
   <si>
     <t>(Optional) Temperature at which sample was stored, e.g. -80 (Units: °C)</t>
   </si>
   <si>
-    <t>sample storage location</t>
+    <t>sample_storage_location</t>
   </si>
   <si>
     <t>(Optional) Location at which sample was stored, usually name of a specific freezer/room. indicate the location name.</t>
   </si>
   <si>
-    <t>size-fraction lower threshold</t>
-  </si>
-  <si>
-    <t>(Optional) Refers to the mesh/pore size used to retain the sample. materials smaller than the size threshold are excluded from the sample (Units: µm)</t>
-  </si>
-  <si>
-    <t>size-fraction upper threshold</t>
-  </si>
-  <si>
-    <t>(Optional) Refers to the mesh/pore size used to pre-filter/pre-sort the sample. materials larger than the size threshold are excluded from the sample (Units: µm)</t>
+    <t>sizefraction_lower_threshold</t>
+  </si>
+  <si>
+    <t>(Optional) Refers to the mesh/pore size used to retain the sample. materials smaller than the size threshold are excluded from the sample (Units: nm)</t>
+  </si>
+  <si>
+    <t>sizefraction_upper_threshold</t>
+  </si>
+  <si>
+    <t>(Optional) Refers to the mesh/pore size used to pre-filter/pre-sort the sample. materials larger than the size threshold are excluded from the sample (Units: nm)</t>
   </si>
   <si>
     <t>aerobic</t>
@@ -1044,7 +1047,7 @@
     <t>anaerobic</t>
   </si>
   <si>
-    <t>oxygenation status of sample</t>
+    <t>oxygenation_status_of_sample</t>
   </si>
   <si>
     <t>(Optional) Oxygenation status of sample</t>
@@ -1056,7 +1059,7 @@
     <t>(Optional) Density of sample (Units: g/m3)</t>
   </si>
   <si>
-    <t>project name</t>
+    <t>project_name</t>
   </si>
   <si>
     <t>(Mandatory) Name of the project within which the sequencing was organized</t>
@@ -1068,37 +1071,37 @@
     <t>(Optional) The ploidy level of the genome (e.g. allopolyploid, haploid, diploid, triploid, tetraploid). it has implications for the downstream study of duplicated gene and regions of the genomes (and perhaps for difficulties in assembly). for terms, please select terms listed under class ploidy (pato:001374) of phenotypic quality ontology (pato), and for a browser of pato (v 2018-03-27) please refer to http://purl.bioontology.org/ontology/pato</t>
   </si>
   <si>
-    <t>number of replicons</t>
+    <t>number_of_replicons</t>
   </si>
   <si>
     <t>(Optional) Reports the number of replicons in a nuclear genome of eukaryotes, in the genome of a bacterium or archaea or the number of segments in a segmented virus. always applied to the haploid chromosome count of a eukaryote. mandatory for migs of eukaryotes, bacteria, archaea and segmented virus.</t>
   </si>
   <si>
-    <t>extrachromosomal elements</t>
+    <t>extrachromosomal_elements</t>
   </si>
   <si>
     <t>(Optional) Do plasmids exist of significant phenotypic consequence (e.g. ones that determine virulence or antibiotic resistance). megaplasmids? other plasmids (borrelia has 15+ plasmids).</t>
   </si>
   <si>
-    <t>estimated size</t>
+    <t>estimated_size</t>
   </si>
   <si>
     <t>(Optional) The estimated size of the genome (in bp) prior to sequencing. of particular importance in the sequencing of (eukaryotic) genome which could remain in draft form for a long or unspecified period. mandatory for migs of eukaryotes.</t>
   </si>
   <si>
-    <t>target gene</t>
+    <t>target_gene</t>
   </si>
   <si>
     <t>(Optional) Targeted gene or locus name for marker gene studies</t>
   </si>
   <si>
-    <t>target subfragment</t>
+    <t>target_subfragment</t>
   </si>
   <si>
     <t>(Optional) Name of subfragment of a gene or locus. important to e.g. identify special regions on marker genes like v6 on 16s rrna</t>
   </si>
   <si>
-    <t>multiplex identifiers</t>
+    <t>multiplex_identifiers</t>
   </si>
   <si>
     <t>(Optional) Molecular barcodes, called multiplex identifiers (mids), that are used to specifically tag unique samples in a sequencing run. sequence should be reported in uppercase letters</t>
@@ -1113,31 +1116,31 @@
     <t>software</t>
   </si>
   <si>
-    <t>sequence quality check</t>
+    <t>sequence_quality_check</t>
   </si>
   <si>
     <t>(Optional) Indicate if the sequence has been called by automatic systems (none) or undergone a manual editing procedure (e.g. by inspecting the raw data or chromatograms). applied only for sequences that are not submitted to sra or dra</t>
   </si>
   <si>
-    <t>chimera check software</t>
+    <t>chimera_check_software</t>
   </si>
   <si>
     <t>(Optional) Tool(s) used for chimera checking, including version number and parameters, to discover and remove chimeric sequences. a chimeric sequence is comprised of two or more phylogenetically distinct parent sequences.</t>
   </si>
   <si>
-    <t>relevant electronic resources</t>
+    <t>relevant_electronic_resources</t>
   </si>
   <si>
     <t>(Optional) A related resource that is referenced, cited, or otherwise associated to the sequence in the format of a pmid, doi or url</t>
   </si>
   <si>
-    <t>relevant standard operating procedures</t>
+    <t>relevant_standard_operating_procedures</t>
   </si>
   <si>
     <t>(Optional) Standard operating procedures used in assembly and/or annotation of genomes, metagenomes or environmental sequences in the format of a pmid, doi or url</t>
   </si>
   <si>
-    <t>collection date</t>
+    <t>collection_date</t>
   </si>
   <si>
     <t>(Mandatory) The date the sample was collected with the intention of sequencing, either as an instance (single point in time) or interval. in case no exact time is available, the date/time can be right truncated i.e. all of these are valid iso8601 compliant times: 2008-01-23t19:23:10+00:00; 2008-01-23t19:23:10; 2008-01-23; 2008-01; 2008.</t>
@@ -1149,37 +1152,37 @@
     <t>(Optional) The altitude of the sample is the vertical distance between earth's surface above sea level and the sampled position in the air. (Units: m)</t>
   </si>
   <si>
-    <t>geographic location (latitude)</t>
+    <t>geographic_location_latitude</t>
   </si>
   <si>
     <t>(Mandatory) The geographical origin of the sample as defined by latitude. the values should be reported in decimal degrees and in wgs84 system (Units: DD)</t>
   </si>
   <si>
-    <t>geographic location (longitude)</t>
+    <t>geographic_location_longitude</t>
   </si>
   <si>
     <t>(Mandatory) The geographical origin of the sample as defined by longitude. the values should be reported in decimal degrees and in wgs84 system (Units: DD)</t>
   </si>
   <si>
-    <t>geographic location (region and locality)</t>
+    <t>geographic_location_region_and_locality</t>
   </si>
   <si>
     <t>(Optional) The geographical origin of the sample as defined by the specific region name followed by the locality name.</t>
   </si>
   <si>
-    <t>broad-scale environmental context</t>
+    <t>broadscale_environmental_context</t>
   </si>
   <si>
     <t>(Mandatory) Report the major environmental system the sample or specimen came from. the system(s) identified should have a coarse spatial grain, to provide the general environmental context of where the sampling was done (e.g. in the desert or a rainforest). we recommend using subclasses of envo’s biome class: http://purl.obolibrary.org/obo/envo_00000428. envo documentation about how to use the field: https://github.com/environmentontology/envo/wiki/using-envo-with-mixs.</t>
   </si>
   <si>
-    <t>local environmental context</t>
+    <t>local_environmental_context</t>
   </si>
   <si>
     <t>(Mandatory) Report the entity or entities which are in the sample or specimen’s local vicinity and which you believe have significant causal influences on your sample or specimen. we recommend using envo terms which are of smaller spatial grain than your entry for "broad-scale environmental context". terms, such as anatomical sites, from other obo library ontologies which interoperate with envo (e.g. uberon) are accepted in this field. envo documentation about how to use the field: https://github.com/environmentontology/envo/wiki/using-envo-with-mixs.</t>
   </si>
   <si>
-    <t>environmental medium</t>
+    <t>environmental_medium</t>
   </si>
   <si>
     <t>(Mandatory) Report the environmental material(s) immediately surrounding the sample or specimen at the time of sampling. we recommend using subclasses of 'environmental material' (http://purl.obolibrary.org/obo/envo_00010483). envo documentation about how to use the field: https://github.com/environmentontology/envo/wiki/using-envo-with-mixs . terms from other obo ontologies are permissible as long as they reference mass/volume nouns (e.g. air, water, blood) and not discrete, countable entities (e.g. a tree, a leaf, a table top).</t>
@@ -1191,25 +1194,25 @@
     <t>(Optional) The elevation of the sampling site as measured by the vertical distance from mean sea level. (Units: m)</t>
   </si>
   <si>
-    <t>amount or size of sample collected</t>
-  </si>
-  <si>
-    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: m3)</t>
+    <t>amount_or_size_of_sample_collected</t>
+  </si>
+  <si>
+    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: kg)</t>
   </si>
   <si>
     <t>biomass</t>
   </si>
   <si>
-    <t>(Optional) Amount of biomass; should include the name for the part of biomass measured, e.g. microbial, total. can include multiple measurements (Units: t)</t>
-  </si>
-  <si>
-    <t>organism count</t>
+    <t>(Optional) Amount of biomass; should include the name for the part of biomass measured, e.g. microbial, total. can include multiple measurements (Units: kg)</t>
+  </si>
+  <si>
+    <t>organism_count</t>
   </si>
   <si>
     <t>(Optional) Total cell count of any organism (or group of organisms) per gram, volume or area of sample, should include name of organism followed by count. the method that was used for the enumeration (e.g. qpcr, atp, mpn, etc.) should also be provided. (example: total prokaryotes; 3.5e7 cells per ml; qpcr)</t>
   </si>
   <si>
-    <t>sample storage duration</t>
+    <t>sample_storage_duration</t>
   </si>
   <si>
     <t>(Optional) Duration for which the sample was stored. indicate the duration for which the sample was stored written in iso 8601 format.</t>
@@ -1428,9 +1431,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1449,6 +1449,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1650,6 +1653,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1659,9 +1665,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1701,7 +1704,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1770,6 +1773,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1845,6 +1851,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1866,6 +1875,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1911,6 +1923,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1923,6 +1938,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1932,9 +1950,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -1959,6 +1974,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2019,12 +2037,12 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
   </si>
   <si>
-    <t>Wake Island</t>
-  </si>
-  <si>
     <t>Wallis and Futuna</t>
   </si>
   <si>
@@ -2082,25 +2100,25 @@
     <t>restricted access</t>
   </si>
   <si>
-    <t>geographic location (country and/or sea)</t>
+    <t>geographic_location_country_andor_sea</t>
   </si>
   <si>
     <t>(Mandatory) The geographical origin of where the sample was collected from, with the intention of sequencing, as defined by the country or sea name. country or sea names should be chosen from the insdc country list (http://insdc.org/country.html).</t>
   </si>
   <si>
-    <t>host disease status</t>
+    <t>host_disease_status</t>
   </si>
   <si>
     <t>(Optional) List of diseases with which the host has been diagnosed; can include multiple diagnoses. the value of the field depends on host; for humans the terms should be chosen from do (disease ontology) at http://www.disease-ontology.org, other hosts are free text</t>
   </si>
   <si>
-    <t>host scientific name</t>
+    <t>host_scientific_name</t>
   </si>
   <si>
     <t>(Optional) Scientific name of the natural (as opposed to laboratory) host to the organism from which sample was obtained.</t>
   </si>
   <si>
-    <t>atmospheric data</t>
+    <t>atmospheric_data</t>
   </si>
   <si>
     <t>(Optional) Measurement of atmospheric data; can include multiple data</t>
@@ -2112,10 +2130,10 @@
     <t>(Optional) Electrical conductivity of water (Units: mS/cm)</t>
   </si>
   <si>
-    <t>water current</t>
-  </si>
-  <si>
-    <t>(Optional) Measurement of magnitude and direction of flow within a fluid (Units: m3/s)</t>
+    <t>water_current</t>
+  </si>
+  <si>
+    <t>(Optional) Measurement of magnitude and direction of flow within a fluid (Units: knot)</t>
   </si>
   <si>
     <t>fluorescence</t>
@@ -2124,31 +2142,31 @@
     <t>(Optional) Raw (volts) or converted (mg chla/m^3) fluorescence of the water (Units: mg Chla/m3)</t>
   </si>
   <si>
-    <t>light intensity</t>
+    <t>light_intensity</t>
   </si>
   <si>
     <t>(Optional) Measurement of light intensity (Units: lux)</t>
   </si>
   <si>
-    <t>mean friction velocity</t>
+    <t>mean_friction_velocity</t>
   </si>
   <si>
     <t>(Optional) Measurement of mean friction velocity (Units: m/s)</t>
   </si>
   <si>
-    <t>mean peak friction velocity</t>
+    <t>mean_peak_friction_velocity</t>
   </si>
   <si>
     <t>(Optional) Measurement of mean peak friction velocity (Units: m/s)</t>
   </si>
   <si>
-    <t>downward PAR</t>
+    <t>downward_par</t>
   </si>
   <si>
     <t>(Optional) Visible waveband radiance and irradiance measurements in the water column (Units: µE/m2/s)</t>
   </si>
   <si>
-    <t>photon flux</t>
+    <t>photon_flux</t>
   </si>
   <si>
     <t>(Optional) Measurement of photon flux (Units: µmol/m2/s)</t>
@@ -2157,7 +2175,7 @@
     <t>pressure</t>
   </si>
   <si>
-    <t>(Optional) Pressure to which the sample is subject, in atmospheres (Units: bar)</t>
+    <t>(Optional) Pressure to which the sample is subject, in atmospheres (Units: atm)</t>
   </si>
   <si>
     <t>temperature</t>
@@ -2172,7 +2190,7 @@
     <t>low</t>
   </si>
   <si>
-    <t>tidal stage</t>
+    <t>tidal_stage</t>
   </si>
   <si>
     <t>(Optional) Stage of tide</t>
@@ -2184,25 +2202,25 @@
     <t>(Optional) Turbidity measurement (Units: NTU)</t>
   </si>
   <si>
-    <t>pH</t>
+    <t>ph</t>
   </si>
   <si>
     <t>(Optional) Ph measurement</t>
   </si>
   <si>
-    <t>total depth of water column</t>
+    <t>total_depth_of_water_column</t>
   </si>
   <si>
     <t>(Optional) Measurement of total depth of water column (Units: m)</t>
   </si>
   <si>
-    <t>alkyl diethers</t>
+    <t>alkyl_diethers</t>
   </si>
   <si>
     <t>(Optional) Concentration of alkyl diethers (Units: µg/L)</t>
   </si>
   <si>
-    <t>aminopeptidase activity</t>
+    <t>aminopeptidase_activity</t>
   </si>
   <si>
     <t>(Optional) Measurement of aminopeptidase activity (Units: mol/L/h)</t>
@@ -2214,19 +2232,19 @@
     <t>(Optional) Concentration of ammonium (Units: µmol/L)</t>
   </si>
   <si>
-    <t>bacterial carbon production</t>
+    <t>bacterial_carbon_production</t>
   </si>
   <si>
     <t>(Optional) Measurement of bacterial carbon production (Units: ng/h)</t>
   </si>
   <si>
-    <t>bacterial production</t>
+    <t>bacterial_production</t>
   </si>
   <si>
     <t>(Optional) Bacterial production in the water column measured by isotope uptake (Units: mg/m3/d)</t>
   </si>
   <si>
-    <t>bacterial respiration</t>
+    <t>bacterial_respiration</t>
   </si>
   <si>
     <t>(Optional) Measurement of bacterial respiration in the water column (Units: mg/m3/d)</t>
@@ -2235,7 +2253,7 @@
     <t>bishomohopanol</t>
   </si>
   <si>
-    <t>(Optional) Concentration of bishomohopanol (Units: µg/g)</t>
+    <t>(Optional) Concentration of bishomohopanol (Units: µg/L)</t>
   </si>
   <si>
     <t>bromide</t>
@@ -2247,10 +2265,10 @@
     <t>calcium</t>
   </si>
   <si>
-    <t>(Optional) Concentration of calcium (Units: µmol/L)</t>
-  </si>
-  <si>
-    <t>carbon/nitrogen ratio</t>
+    <t>(Optional) Concentration of calcium (Units: mg/L)</t>
+  </si>
+  <si>
+    <t>carbonnitrogen_ratio</t>
   </si>
   <si>
     <t>(Optional) Ratio of amount or concentrations of carbon to nitrogen</t>
@@ -2268,61 +2286,61 @@
     <t>(Optional) Concentration of chlorophyll (Units: µg/L)</t>
   </si>
   <si>
-    <t>diether lipids</t>
+    <t>diether_lipids</t>
   </si>
   <si>
     <t>(Optional) Concentration of diether lipids; can include multiple types of diether lipids (Units: ng/L)</t>
   </si>
   <si>
-    <t>dissolved carbon dioxide</t>
+    <t>dissolved_carbon_dioxide</t>
   </si>
   <si>
     <t>(Optional) Concentration of dissolved carbon dioxide (Units: µmol/L)</t>
   </si>
   <si>
-    <t>dissolved hydrogen</t>
+    <t>dissolved_hydrogen</t>
   </si>
   <si>
     <t>(Optional) Concentration of dissolved hydrogen (Units: µmol/L)</t>
   </si>
   <si>
-    <t>dissolved inorganic carbon</t>
+    <t>dissolved_inorganic_carbon</t>
   </si>
   <si>
     <t>(Optional) Dissolved inorganic carbon concentration (Units: µg/L)</t>
   </si>
   <si>
-    <t>dissolved inorganic nitrogen</t>
+    <t>dissolved_inorganic_nitrogen</t>
   </si>
   <si>
     <t>(Optional) Concentration of dissolved inorganic nitrogen (Units: µg/L)</t>
   </si>
   <si>
-    <t>dissolved inorganic phosphorus</t>
+    <t>dissolved_inorganic_phosphorus</t>
   </si>
   <si>
     <t>(Optional) Concentration of dissolved inorganic phosphorus (Units: µg/L)</t>
   </si>
   <si>
-    <t>dissolved organic carbon</t>
+    <t>dissolved_organic_carbon</t>
   </si>
   <si>
     <t>(Optional) Concentration of dissolved organic carbon (Units: µmol/L)</t>
   </si>
   <si>
-    <t>dissolved organic nitrogen</t>
+    <t>dissolved_organic_nitrogen</t>
   </si>
   <si>
     <t>(Optional) Dissolved organic nitrogen concentration measured as; total dissolved nitrogen - nh4 - no3 - no2 (Units: µg/L)</t>
   </si>
   <si>
-    <t>dissolved oxygen</t>
+    <t>dissolved_oxygen</t>
   </si>
   <si>
     <t>(Optional) Concentration of dissolved oxygen (Units: µmol/kg)</t>
   </si>
   <si>
-    <t>glucosidase activity</t>
+    <t>glucosidase_activity</t>
   </si>
   <si>
     <t>(Optional) Measurement of glucosidase activity (Units: mol/L/h)</t>
@@ -2331,10 +2349,10 @@
     <t>magnesium</t>
   </si>
   <si>
-    <t>(Optional) Concentration of magnesium (Units: parts/million)</t>
-  </si>
-  <si>
-    <t>n-alkanes</t>
+    <t>(Optional) Concentration of magnesium (Units: mg/L)</t>
+  </si>
+  <si>
+    <t>nalkanes</t>
   </si>
   <si>
     <t>(Optional) Concentration of n-alkanes; can include multiple n-alkanes (Units: µmol/L)</t>
@@ -2352,43 +2370,43 @@
     <t>(Optional) Concentration of nitrite (Units: µmol/L)</t>
   </si>
   <si>
-    <t>total nitrogen concentration</t>
+    <t>total_nitrogen_concentration</t>
   </si>
   <si>
     <t>(Optional) Concentration of nitrogen (total). total nitrogen concentration of water samples, calculated by: total nitrogen = total dissolved nitrogen + particulate nitrogen. can also be measured without filtering, reported as nitrogen (Units: µmol/L)</t>
   </si>
   <si>
-    <t>organic carbon</t>
+    <t>organic_carbon</t>
   </si>
   <si>
     <t>(Optional) Concentration of organic carbon (Units: µmol/L)</t>
   </si>
   <si>
-    <t>organic matter</t>
+    <t>organic_matter</t>
   </si>
   <si>
     <t>(Optional) Concentration of organic matter (Units: µg/L)</t>
   </si>
   <si>
-    <t>organic nitrogen</t>
+    <t>organic_nitrogen</t>
   </si>
   <si>
     <t>(Optional) Concentration of organic nitrogen (Units: µg/L)</t>
   </si>
   <si>
-    <t>particulate organic carbon</t>
+    <t>particulate_organic_carbon</t>
   </si>
   <si>
     <t>(Optional) Concentration of particulate organic carbon (Units: µg/L)</t>
   </si>
   <si>
-    <t>particulate organic nitrogen</t>
+    <t>particulate_organic_nitrogen</t>
   </si>
   <si>
     <t>(Optional) Concentration of particulate organic nitrogen (Units: µg/L)</t>
   </si>
   <si>
-    <t>petroleum hydrocarbon</t>
+    <t>petroleum_hydrocarbon</t>
   </si>
   <si>
     <t>(Optional) Concentration of petroleum hydrocarbon (Units: µmol/L)</t>
@@ -2406,7 +2424,7 @@
     <t>(Optional) Concentration of phosphate (Units: µmol/L)</t>
   </si>
   <si>
-    <t>phospholipid fatty acid</t>
+    <t>phospholipid_fatty_acid</t>
   </si>
   <si>
     <t>(Optional) Concentration of phospholipid fatty acids; can include multiple values (Units: mol/g)</t>
@@ -2418,13 +2436,13 @@
     <t>(Optional) Concentration of potassium (Units: µmol/L)</t>
   </si>
   <si>
-    <t>primary production</t>
-  </si>
-  <si>
-    <t>(Optional) Measurement of primary production (Units: mg/m3/day)</t>
-  </si>
-  <si>
-    <t>redox potential</t>
+    <t>primary_production</t>
+  </si>
+  <si>
+    <t>(Optional) Measurement of primary production (Units: g/m2/day)</t>
+  </si>
+  <si>
+    <t>redox_potential</t>
   </si>
   <si>
     <t>(Optional) Redox potential, measured relative to a hydrogen cell, indicating oxidation or reduction potential (Units: mV)</t>
@@ -2448,7 +2466,7 @@
     <t>(Optional) Sodium concentration (Units: µmol/L)</t>
   </si>
   <si>
-    <t>soluble reactive phosphorus</t>
+    <t>soluble_reactive_phosphorus</t>
   </si>
   <si>
     <t>(Optional) Concentration of soluble reactive phosphorus (Units: µmol/L)</t>
@@ -2457,52 +2475,52 @@
     <t>sulfate</t>
   </si>
   <si>
-    <t>(Optional) Concentration of sulfate (Units: µmol/L)</t>
+    <t>(Optional) Concentration of sulfate (Units: mg/L)</t>
   </si>
   <si>
     <t>sulfide</t>
   </si>
   <si>
-    <t>(Optional) Concentration of sulfide (Units: µmol/L)</t>
-  </si>
-  <si>
-    <t>suspended particulate matter</t>
+    <t>(Optional) Concentration of sulfide (Units: mg/L)</t>
+  </si>
+  <si>
+    <t>suspended_particulate_matter</t>
   </si>
   <si>
     <t>(Optional) Concentration of suspended particulate matter (Units: mg/L)</t>
   </si>
   <si>
-    <t>total dissolved nitrogen</t>
+    <t>total_dissolved_nitrogen</t>
   </si>
   <si>
     <t>(Optional) Total dissolved nitrogen concentration, reported as nitrogen, measured by: total dissolved nitrogen = nh4 + no3no2 + dissolved organic nitrogen (Units: µg/L)</t>
   </si>
   <si>
-    <t>total inorganic nitrogen</t>
+    <t>total_inorganic_nitrogen</t>
   </si>
   <si>
     <t>(Optional) Total inorganic nitrogen content (Units: µg/L)</t>
   </si>
   <si>
-    <t>total nitrogen content</t>
-  </si>
-  <si>
-    <t>(Optional) Total nitrogen content of the sample (Units: µmol/L)</t>
-  </si>
-  <si>
-    <t>total particulate carbon</t>
-  </si>
-  <si>
-    <t>(Optional) Total particulate carbon content (Units: µmol/L)</t>
-  </si>
-  <si>
-    <t>total phosphorus</t>
+    <t>total_nitrogen_content</t>
+  </si>
+  <si>
+    <t>(Optional) Total nitrogen content of the sample (Units: µg/L)</t>
+  </si>
+  <si>
+    <t>total_particulate_carbon</t>
+  </si>
+  <si>
+    <t>(Optional) Total particulate carbon content (Units: µg/L)</t>
+  </si>
+  <si>
+    <t>total_phosphorus</t>
   </si>
   <si>
     <t>(Optional) Total phosphorus concentration, calculated by: total phosphorus = total dissolved phosphorus + particulate phosphorus. can also be measured without filtering, reported as phosphorus (Units: µmol/L)</t>
   </si>
   <si>
-    <t>alkalinity method</t>
+    <t>alkalinity_method</t>
   </si>
   <si>
     <t>(Optional) Method used for alkalinity measurement (Units: m2)</t>
@@ -2514,7 +2532,7 @@
     <t>(Optional) Alkalinity, the ability of a solution to neutralize acids to the equivalence point of carbonate or bicarbonate (Units: mEq/L)</t>
   </si>
   <si>
-    <t>source material identifiers</t>
+    <t>source_material_identifiers</t>
   </si>
   <si>
     <t>(Optional) A unique identifier assigned to a material sample (as defined by http://rs.tdwg.org/dwc/terms/materialsampleid, and as opposed to a particular digital record of a material sample) used for extracting nucleic acids, and subsequent sequencing. the identifier can refer either to the original material collected or to any derived sub-samples. the insdc qualifiers /specimen_voucher, /bio_material, or /culture_collection may or may not share the same value as the source_mat_id field. for instance, the /specimen_voucher qualifier and source_mat_id may both contain 'uam:herps:14' , referring to both the specimen voucher and sampled tissue with the same identifier. however, the /culture_collection qualifier may refer to a value from an initial culture (e.g. atcc:11775) while source_mat_id would refer to an identifier from some derived culture from which the nucleic acids were extracted (e.g. xatc123 or ark:/2154/r2).</t>
@@ -2526,121 +2544,121 @@
     <t>(Optional) Type of perturbation, e.g. chemical administration, physical disturbance, etc., coupled with time that perturbation occurred; can include multiple perturbation types</t>
   </si>
   <si>
-    <t>negative control type</t>
+    <t>negative_control_type</t>
   </si>
   <si>
     <t>(Optional) The substance or equipment used as a negative control in an investigation</t>
   </si>
   <si>
-    <t>positive control type</t>
+    <t>positive_control_type</t>
   </si>
   <si>
     <t>(Optional) The substance, mixture, product, or apparatus used to verify that a process which is part of an investigation delivers a true positive.</t>
   </si>
   <si>
-    <t>experimental factor</t>
+    <t>experimental_factor</t>
   </si>
   <si>
     <t>(Optional) Experimental factors are essentially the variable aspects of an experiment design which can be used to describe an experiment, or set of experiments, in an increasingly detailed manner. this field accepts ontology terms from experimental factor ontology (efo) and/or ontology for biomedical investigations (obi). for a browser of efo (v 2.95) terms, please see http://purl.bioontology.org/ontology/efo; for a browser of obi (v 2018-02-12) terms please see http://purl.bioontology.org/ontology/obi. e.g. time series design [efo:efo_0001779]</t>
   </si>
   <si>
-    <t>encoded traits</t>
+    <t>encoded_traits</t>
   </si>
   <si>
     <t>(Optional) Should include key traits like antibiotic resistance or xenobiotic degradation phenotypes for plasmids, converting genes for phage</t>
   </si>
   <si>
-    <t>subspecific genetic lineage</t>
+    <t>subspecific_genetic_lineage</t>
   </si>
   <si>
     <t>(Optional) Information about the genetic distinctness of the sequenced organism below the subspecies level, e.g., serovar, serotype, biotype, ecotype, or any relevant genetic typing schemes like group i plasmid. subspecies should not be recorded in this term, but in the ncbi taxonomy. supply both the lineage name and the lineage rank separated by a colon, e.g., biovar:abc123.</t>
   </si>
   <si>
-    <t>taxonomic classification</t>
+    <t>taxonomic_classification</t>
   </si>
   <si>
     <t>(Optional) Method used for taxonomic classification, along with reference database used, classification rank, and thresholds used to classify new genomes. expected values are: classification method, database name, and other parameters e.g. vcontact vcontact2 (references from ncbi refseq v83, genus rank classification, default parameters)</t>
   </si>
   <si>
-    <t>isolation and growth condition</t>
+    <t>isolation_and_growth_condition</t>
   </si>
   <si>
     <t>(Optional) Publication reference in the form of pubmed id (pmid), digital object identifier (doi) or url for isolation and growth condition specifications of the organism/material. mandatory for migs and mimarks specimen.</t>
   </si>
   <si>
-    <t>annotation source</t>
+    <t>annotation_source</t>
   </si>
   <si>
     <t>(Optional) For cases where annotation was provided by a community jamboree or model organism database rather than by a specific submitter</t>
   </si>
   <si>
-    <t>reference for biomaterial</t>
+    <t>reference_for_biomaterial</t>
   </si>
   <si>
     <t>(Optional) Primary publication if isolated before genome publication; otherwise, primary genome report. mandatory for migs of bacteria and archaea.</t>
   </si>
   <si>
-    <t>sample material processing</t>
+    <t>sample_material_processing</t>
   </si>
   <si>
     <t>(Optional) A brief description of any processing applied to the sample during or after retrieving the sample from environment, or a link to the relevant protocol(s) performed.</t>
   </si>
   <si>
-    <t>sample volume or weight for DNA extraction</t>
-  </si>
-  <si>
-    <t>(Optional) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: ng)</t>
-  </si>
-  <si>
-    <t>nucleic acid extraction</t>
+    <t>sample_volume_or_weight_for_dna_extraction</t>
+  </si>
+  <si>
+    <t>(Optional) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: mL)</t>
+  </si>
+  <si>
+    <t>nucleic_acid_extraction</t>
   </si>
   <si>
     <t>(Optional) A link to a literature reference, electronic resource or a standard operating procedure (sop), that describes the material separation to recover the nucleic acid fraction from a sample</t>
   </si>
   <si>
-    <t>nucleic acid amplification</t>
+    <t>nucleic_acid_amplification</t>
   </si>
   <si>
     <t>(Optional) A link to a literature reference, electronic resource or a standard operating procedure (sop), that describes the enzymatic amplification (pcr, tma, nasba) of specific nucleic acids</t>
   </si>
   <si>
-    <t>library size</t>
+    <t>library_size</t>
   </si>
   <si>
     <t>(Optional) Total number of clones in the library prepared for the project</t>
   </si>
   <si>
-    <t>library reads sequenced</t>
+    <t>library_reads_sequenced</t>
   </si>
   <si>
     <t>(Optional) Total number of clones sequenced from the library</t>
   </si>
   <si>
-    <t>library construction method</t>
+    <t>library_construction_method</t>
   </si>
   <si>
     <t>(Optional) Library construction method used for clone libraries</t>
   </si>
   <si>
-    <t>library vector</t>
+    <t>library_vector</t>
   </si>
   <si>
     <t>(Optional) Cloning vector type(s) used in construction of libraries</t>
   </si>
   <si>
-    <t>library screening strategy</t>
+    <t>library_screening_strategy</t>
   </si>
   <si>
     <t>(Optional) Specific enrichment or screening methods applied before and/or after creating clone libraries in order to select a specific group of sequences</t>
   </si>
   <si>
-    <t>pcr conditions</t>
+    <t>pcr_conditions</t>
   </si>
   <si>
     <t>(Optional) Description of reaction conditions and components for pcr in the form of 'initial denaturation:94degc_1.5min; annealing=...'</t>
   </si>
   <si>
-    <t>pcr primers</t>
+    <t>pcr_primers</t>
   </si>
   <si>
     <t>(Optional) Pcr primers that were used to amplify the sequence of the targeted gene, locus or subfragment. this field should contain all the primers used for a single pcr reaction if multiple forward or reverse primers are present in a single pcr reaction. the primer sequence should be reported in uppercase letters</t>
@@ -2655,10 +2673,10 @@
     <t>depth</t>
   </si>
   <si>
-    <t>(Mandatory) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: mm)</t>
-  </si>
-  <si>
-    <t>chemical administration</t>
+    <t>(Mandatory) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: m)</t>
+  </si>
+  <si>
+    <t>chemical_administration</t>
   </si>
   <si>
     <t>(Optional) List of chemical compounds administered to the host or site where sampling occurred, and when (e.g. antibiotics, n fertilizer, air filter); can include multiple compounds. for chemical entities of biological interest ontology (chebi) (v111), please see http://purl.bioontology.org/ontology/chebi</t>
@@ -3191,7 +3209,7 @@
         <v>143</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3235,7 +3253,7 @@
         <v>144</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -3262,7 +3280,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N86"/>
+  <dimension ref="G1:N87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3986,6 +4004,11 @@
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="87" spans="14:14">
+      <c r="N87" t="s">
         <v>117</v>
       </c>
     </row>
@@ -4007,27 +4030,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4047,122 +4070,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -4186,828 +4209,828 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>799</v>
+        <v>805</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>833</v>
+        <v>839</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="DP1" s="1" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="DQ1" s="1" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="DR1" s="1" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="DS1" s="1" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="DU1" s="1" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="DV1" s="1" t="s">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="DW1" s="1" t="s">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>873</v>
+        <v>879</v>
       </c>
     </row>
     <row r="2" spans="1:138" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>784</v>
+        <v>790</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>796</v>
+        <v>802</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>800</v>
+        <v>806</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>812</v>
+        <v>818</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>830</v>
+        <v>836</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="DN2" s="2" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="DO2" s="2" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="DP2" s="2" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="DQ2" s="2" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="DR2" s="2" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="DS2" s="2" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="DT2" s="2" t="s">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="DU2" s="2" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
       <c r="DV2" s="2" t="s">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="DW2" s="2" t="s">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="DX2" s="2" t="s">
-        <v>854</v>
+        <v>860</v>
       </c>
       <c r="DY2" s="2" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="DZ2" s="2" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="EA2" s="2" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="EB2" s="2" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="EC2" s="2" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="ED2" s="2" t="s">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="EE2" s="2" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="EF2" s="2" t="s">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="EG2" s="2" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="EH2" s="2" t="s">
-        <v>874</v>
+        <v>880</v>
       </c>
     </row>
   </sheetData>
@@ -5040,1599 +5063,1624 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="E1:BE289"/>
+  <dimension ref="E1:BE294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="5:57">
       <c r="E1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Z1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AQ1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="BE1" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
     </row>
     <row r="2" spans="5:57">
       <c r="E2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Z2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AQ2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="BE2" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
     </row>
     <row r="3" spans="5:57">
       <c r="E3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Z3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AQ3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4" spans="5:57">
       <c r="E4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AQ4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="5" spans="5:57">
       <c r="E5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AQ5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="6" spans="5:57">
       <c r="E6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AQ6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="7" spans="5:57">
       <c r="E7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AQ7" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="8" spans="5:57">
       <c r="E8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AQ8" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9" spans="5:57">
       <c r="E9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AQ9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="10" spans="5:57">
       <c r="E10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AQ10" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="11" spans="5:57">
       <c r="E11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AQ11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="12" spans="5:57">
       <c r="E12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AQ12" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="13" spans="5:57">
       <c r="E13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AQ13" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="14" spans="5:57">
       <c r="E14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AQ14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="15" spans="5:57">
       <c r="E15" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AQ15" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="16" spans="5:57">
       <c r="E16" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AQ16" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="17" spans="5:43">
       <c r="E17" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AQ17" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="18" spans="5:43">
       <c r="E18" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AQ18" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="19" spans="5:43">
       <c r="E19" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AQ19" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="20" spans="5:43">
       <c r="E20" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AQ20" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="21" spans="5:43">
       <c r="E21" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AQ21" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="22" spans="5:43">
       <c r="E22" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AQ22" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="23" spans="5:43">
       <c r="E23" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AQ23" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="24" spans="5:43">
       <c r="E24" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AQ24" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="25" spans="5:43">
       <c r="E25" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AQ25" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="26" spans="5:43">
       <c r="E26" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AQ26" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="27" spans="5:43">
       <c r="E27" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AQ27" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="28" spans="5:43">
       <c r="E28" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AQ28" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="29" spans="5:43">
       <c r="E29" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AQ29" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="30" spans="5:43">
       <c r="E30" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AQ30" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="31" spans="5:43">
       <c r="AQ31" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="32" spans="5:43">
       <c r="AQ32" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="33" spans="43:43">
       <c r="AQ33" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="34" spans="43:43">
       <c r="AQ34" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="35" spans="43:43">
       <c r="AQ35" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="36" spans="43:43">
       <c r="AQ36" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="37" spans="43:43">
       <c r="AQ37" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="38" spans="43:43">
       <c r="AQ38" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="39" spans="43:43">
       <c r="AQ39" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="40" spans="43:43">
       <c r="AQ40" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="41" spans="43:43">
       <c r="AQ41" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="42" spans="43:43">
       <c r="AQ42" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="43" spans="43:43">
       <c r="AQ43" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="44" spans="43:43">
       <c r="AQ44" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="45" spans="43:43">
       <c r="AQ45" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="46" spans="43:43">
       <c r="AQ46" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="47" spans="43:43">
       <c r="AQ47" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="48" spans="43:43">
       <c r="AQ48" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="49" spans="43:43">
       <c r="AQ49" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="50" spans="43:43">
       <c r="AQ50" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="51" spans="43:43">
       <c r="AQ51" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="52" spans="43:43">
       <c r="AQ52" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="53" spans="43:43">
       <c r="AQ53" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="54" spans="43:43">
       <c r="AQ54" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="55" spans="43:43">
       <c r="AQ55" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="56" spans="43:43">
       <c r="AQ56" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="57" spans="43:43">
       <c r="AQ57" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="58" spans="43:43">
       <c r="AQ58" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="59" spans="43:43">
       <c r="AQ59" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="60" spans="43:43">
       <c r="AQ60" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="61" spans="43:43">
       <c r="AQ61" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="62" spans="43:43">
       <c r="AQ62" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="63" spans="43:43">
       <c r="AQ63" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="64" spans="43:43">
       <c r="AQ64" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="65" spans="43:43">
       <c r="AQ65" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="66" spans="43:43">
       <c r="AQ66" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="67" spans="43:43">
       <c r="AQ67" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="68" spans="43:43">
       <c r="AQ68" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="69" spans="43:43">
       <c r="AQ69" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="70" spans="43:43">
       <c r="AQ70" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="71" spans="43:43">
       <c r="AQ71" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="72" spans="43:43">
       <c r="AQ72" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="73" spans="43:43">
       <c r="AQ73" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="74" spans="43:43">
       <c r="AQ74" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="75" spans="43:43">
       <c r="AQ75" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="76" spans="43:43">
       <c r="AQ76" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="77" spans="43:43">
       <c r="AQ77" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="78" spans="43:43">
       <c r="AQ78" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="79" spans="43:43">
       <c r="AQ79" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="80" spans="43:43">
       <c r="AQ80" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="81" spans="43:43">
       <c r="AQ81" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="82" spans="43:43">
       <c r="AQ82" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="83" spans="43:43">
       <c r="AQ83" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="84" spans="43:43">
       <c r="AQ84" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="85" spans="43:43">
       <c r="AQ85" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="86" spans="43:43">
       <c r="AQ86" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="87" spans="43:43">
       <c r="AQ87" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="88" spans="43:43">
       <c r="AQ88" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="89" spans="43:43">
       <c r="AQ89" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="90" spans="43:43">
       <c r="AQ90" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="91" spans="43:43">
       <c r="AQ91" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="92" spans="43:43">
       <c r="AQ92" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="93" spans="43:43">
       <c r="AQ93" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="94" spans="43:43">
       <c r="AQ94" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="95" spans="43:43">
       <c r="AQ95" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="96" spans="43:43">
       <c r="AQ96" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="97" spans="43:43">
       <c r="AQ97" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="98" spans="43:43">
       <c r="AQ98" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="99" spans="43:43">
       <c r="AQ99" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="100" spans="43:43">
       <c r="AQ100" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="101" spans="43:43">
       <c r="AQ101" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="102" spans="43:43">
       <c r="AQ102" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="103" spans="43:43">
       <c r="AQ103" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="104" spans="43:43">
       <c r="AQ104" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="105" spans="43:43">
       <c r="AQ105" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="106" spans="43:43">
       <c r="AQ106" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="107" spans="43:43">
       <c r="AQ107" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="108" spans="43:43">
       <c r="AQ108" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="109" spans="43:43">
       <c r="AQ109" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="110" spans="43:43">
       <c r="AQ110" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="111" spans="43:43">
       <c r="AQ111" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="112" spans="43:43">
       <c r="AQ112" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="113" spans="43:43">
       <c r="AQ113" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="114" spans="43:43">
       <c r="AQ114" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="115" spans="43:43">
       <c r="AQ115" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="116" spans="43:43">
       <c r="AQ116" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="117" spans="43:43">
       <c r="AQ117" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="118" spans="43:43">
       <c r="AQ118" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="119" spans="43:43">
       <c r="AQ119" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="120" spans="43:43">
       <c r="AQ120" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="121" spans="43:43">
       <c r="AQ121" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="122" spans="43:43">
       <c r="AQ122" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="123" spans="43:43">
       <c r="AQ123" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="124" spans="43:43">
       <c r="AQ124" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="125" spans="43:43">
       <c r="AQ125" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="126" spans="43:43">
       <c r="AQ126" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="127" spans="43:43">
       <c r="AQ127" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="128" spans="43:43">
       <c r="AQ128" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="129" spans="43:43">
       <c r="AQ129" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="130" spans="43:43">
       <c r="AQ130" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="131" spans="43:43">
       <c r="AQ131" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="132" spans="43:43">
       <c r="AQ132" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="133" spans="43:43">
       <c r="AQ133" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="134" spans="43:43">
       <c r="AQ134" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="135" spans="43:43">
       <c r="AQ135" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="136" spans="43:43">
       <c r="AQ136" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="137" spans="43:43">
       <c r="AQ137" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="138" spans="43:43">
       <c r="AQ138" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="139" spans="43:43">
       <c r="AQ139" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="140" spans="43:43">
       <c r="AQ140" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="141" spans="43:43">
       <c r="AQ141" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="142" spans="43:43">
       <c r="AQ142" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="143" spans="43:43">
       <c r="AQ143" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="144" spans="43:43">
       <c r="AQ144" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="145" spans="43:43">
       <c r="AQ145" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="146" spans="43:43">
       <c r="AQ146" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="147" spans="43:43">
       <c r="AQ147" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="148" spans="43:43">
       <c r="AQ148" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="149" spans="43:43">
       <c r="AQ149" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="150" spans="43:43">
       <c r="AQ150" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="151" spans="43:43">
       <c r="AQ151" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="152" spans="43:43">
       <c r="AQ152" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="153" spans="43:43">
       <c r="AQ153" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="154" spans="43:43">
       <c r="AQ154" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="155" spans="43:43">
       <c r="AQ155" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="156" spans="43:43">
       <c r="AQ156" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="157" spans="43:43">
       <c r="AQ157" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="158" spans="43:43">
       <c r="AQ158" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="159" spans="43:43">
       <c r="AQ159" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="160" spans="43:43">
       <c r="AQ160" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="161" spans="43:43">
       <c r="AQ161" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="162" spans="43:43">
       <c r="AQ162" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="163" spans="43:43">
       <c r="AQ163" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="164" spans="43:43">
       <c r="AQ164" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="165" spans="43:43">
       <c r="AQ165" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="166" spans="43:43">
       <c r="AQ166" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="167" spans="43:43">
       <c r="AQ167" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="168" spans="43:43">
       <c r="AQ168" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="169" spans="43:43">
       <c r="AQ169" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="170" spans="43:43">
       <c r="AQ170" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="171" spans="43:43">
       <c r="AQ171" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="172" spans="43:43">
       <c r="AQ172" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="173" spans="43:43">
       <c r="AQ173" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="174" spans="43:43">
       <c r="AQ174" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="175" spans="43:43">
       <c r="AQ175" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="176" spans="43:43">
       <c r="AQ176" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="177" spans="43:43">
       <c r="AQ177" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="178" spans="43:43">
       <c r="AQ178" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="179" spans="43:43">
       <c r="AQ179" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="180" spans="43:43">
       <c r="AQ180" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="181" spans="43:43">
       <c r="AQ181" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="182" spans="43:43">
       <c r="AQ182" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="183" spans="43:43">
       <c r="AQ183" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="184" spans="43:43">
       <c r="AQ184" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="185" spans="43:43">
       <c r="AQ185" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="186" spans="43:43">
       <c r="AQ186" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="187" spans="43:43">
       <c r="AQ187" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="188" spans="43:43">
       <c r="AQ188" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="189" spans="43:43">
       <c r="AQ189" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="190" spans="43:43">
       <c r="AQ190" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="191" spans="43:43">
       <c r="AQ191" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="192" spans="43:43">
       <c r="AQ192" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="193" spans="43:43">
       <c r="AQ193" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="194" spans="43:43">
       <c r="AQ194" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="195" spans="43:43">
       <c r="AQ195" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="196" spans="43:43">
       <c r="AQ196" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="197" spans="43:43">
       <c r="AQ197" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="198" spans="43:43">
       <c r="AQ198" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="199" spans="43:43">
       <c r="AQ199" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="200" spans="43:43">
       <c r="AQ200" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="201" spans="43:43">
       <c r="AQ201" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="202" spans="43:43">
       <c r="AQ202" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="203" spans="43:43">
       <c r="AQ203" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="204" spans="43:43">
       <c r="AQ204" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="205" spans="43:43">
       <c r="AQ205" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="206" spans="43:43">
       <c r="AQ206" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="207" spans="43:43">
       <c r="AQ207" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="208" spans="43:43">
       <c r="AQ208" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="209" spans="43:43">
       <c r="AQ209" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="210" spans="43:43">
       <c r="AQ210" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="211" spans="43:43">
       <c r="AQ211" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="212" spans="43:43">
       <c r="AQ212" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="213" spans="43:43">
       <c r="AQ213" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="214" spans="43:43">
       <c r="AQ214" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="215" spans="43:43">
       <c r="AQ215" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="216" spans="43:43">
       <c r="AQ216" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="217" spans="43:43">
       <c r="AQ217" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="218" spans="43:43">
       <c r="AQ218" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="219" spans="43:43">
       <c r="AQ219" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="220" spans="43:43">
       <c r="AQ220" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="221" spans="43:43">
       <c r="AQ221" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="222" spans="43:43">
       <c r="AQ222" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="223" spans="43:43">
       <c r="AQ223" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="224" spans="43:43">
       <c r="AQ224" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="225" spans="43:43">
       <c r="AQ225" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="226" spans="43:43">
       <c r="AQ226" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="227" spans="43:43">
       <c r="AQ227" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="228" spans="43:43">
       <c r="AQ228" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="229" spans="43:43">
       <c r="AQ229" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="230" spans="43:43">
       <c r="AQ230" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="231" spans="43:43">
       <c r="AQ231" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="232" spans="43:43">
       <c r="AQ232" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="233" spans="43:43">
       <c r="AQ233" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="234" spans="43:43">
       <c r="AQ234" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="235" spans="43:43">
       <c r="AQ235" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="236" spans="43:43">
       <c r="AQ236" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="237" spans="43:43">
       <c r="AQ237" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="238" spans="43:43">
       <c r="AQ238" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="239" spans="43:43">
       <c r="AQ239" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="240" spans="43:43">
       <c r="AQ240" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="241" spans="43:43">
       <c r="AQ241" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="242" spans="43:43">
       <c r="AQ242" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="243" spans="43:43">
       <c r="AQ243" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="244" spans="43:43">
       <c r="AQ244" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="245" spans="43:43">
       <c r="AQ245" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="246" spans="43:43">
       <c r="AQ246" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="247" spans="43:43">
       <c r="AQ247" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="248" spans="43:43">
       <c r="AQ248" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="249" spans="43:43">
       <c r="AQ249" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="250" spans="43:43">
       <c r="AQ250" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="251" spans="43:43">
       <c r="AQ251" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="252" spans="43:43">
       <c r="AQ252" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="253" spans="43:43">
       <c r="AQ253" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="254" spans="43:43">
       <c r="AQ254" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="255" spans="43:43">
       <c r="AQ255" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="256" spans="43:43">
       <c r="AQ256" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="257" spans="43:43">
       <c r="AQ257" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="258" spans="43:43">
       <c r="AQ258" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="259" spans="43:43">
       <c r="AQ259" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="260" spans="43:43">
       <c r="AQ260" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="261" spans="43:43">
       <c r="AQ261" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="262" spans="43:43">
       <c r="AQ262" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="263" spans="43:43">
       <c r="AQ263" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="264" spans="43:43">
       <c r="AQ264" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="265" spans="43:43">
       <c r="AQ265" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="266" spans="43:43">
       <c r="AQ266" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="267" spans="43:43">
       <c r="AQ267" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="268" spans="43:43">
       <c r="AQ268" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="269" spans="43:43">
       <c r="AQ269" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="270" spans="43:43">
       <c r="AQ270" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="271" spans="43:43">
       <c r="AQ271" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="272" spans="43:43">
       <c r="AQ272" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="273" spans="43:43">
       <c r="AQ273" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="274" spans="43:43">
       <c r="AQ274" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="275" spans="43:43">
       <c r="AQ275" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="276" spans="43:43">
       <c r="AQ276" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="277" spans="43:43">
       <c r="AQ277" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="278" spans="43:43">
       <c r="AQ278" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="279" spans="43:43">
       <c r="AQ279" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="280" spans="43:43">
       <c r="AQ280" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="281" spans="43:43">
       <c r="AQ281" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="282" spans="43:43">
       <c r="AQ282" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="283" spans="43:43">
       <c r="AQ283" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="284" spans="43:43">
       <c r="AQ284" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="285" spans="43:43">
       <c r="AQ285" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="286" spans="43:43">
       <c r="AQ286" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="287" spans="43:43">
       <c r="AQ287" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="288" spans="43:43">
       <c r="AQ288" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="289" spans="43:43">
       <c r="AQ289" t="s">
-        <v>680</v>
+        <v>681</v>
+      </c>
+    </row>
+    <row r="290" spans="43:43">
+      <c r="AQ290" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="291" spans="43:43">
+      <c r="AQ291" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="292" spans="43:43">
+      <c r="AQ292" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="293" spans="43:43">
+      <c r="AQ293" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="294" spans="43:43">
+      <c r="AQ294" t="s">
+        <v>686</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000024/metadata_template_ERC000024.xlsx
+++ b/templates/ERC000024/metadata_template_ERC000024.xlsx
@@ -1050,13 +1050,13 @@
     <t>size-fraction lower threshold</t>
   </si>
   <si>
-    <t>(Optional) Refers to the mesh/pore size used to retain the sample. materials smaller than the size threshold are excluded from the sample (Units: µm)</t>
+    <t>(Optional) Refers to the mesh/pore size used to retain the sample. materials smaller than the size threshold are excluded from the sample (Units: nm)</t>
   </si>
   <si>
     <t>size-fraction upper threshold</t>
   </si>
   <si>
-    <t>(Optional) Refers to the mesh/pore size used to pre-filter/pre-sort the sample. materials larger than the size threshold are excluded from the sample (Units: µm)</t>
+    <t>(Optional) Refers to the mesh/pore size used to pre-filter/pre-sort the sample. materials larger than the size threshold are excluded from the sample (Units: nm)</t>
   </si>
   <si>
     <t>aerobic</t>
@@ -1215,13 +1215,13 @@
     <t>amount or size of sample collected</t>
   </si>
   <si>
-    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: m3)</t>
+    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: kg)</t>
   </si>
   <si>
     <t>biomass</t>
   </si>
   <si>
-    <t>(Optional) Amount of biomass; should include the name for the part of biomass measured, e.g. microbial, total. can include multiple measurements (Units: t)</t>
+    <t>(Optional) Amount of biomass; should include the name for the part of biomass measured, e.g. microbial, total. can include multiple measurements (Units: kg)</t>
   </si>
   <si>
     <t>organism count</t>
@@ -2151,7 +2151,7 @@
     <t>water current</t>
   </si>
   <si>
-    <t>(Optional) Measurement of magnitude and direction of flow within a fluid (Units: m3/s)</t>
+    <t>(Optional) Measurement of magnitude and direction of flow within a fluid (Units: knot)</t>
   </si>
   <si>
     <t>fluorescence</t>
@@ -2193,7 +2193,7 @@
     <t>pressure</t>
   </si>
   <si>
-    <t>(Optional) Pressure to which the sample is subject, in atmospheres (Units: bar)</t>
+    <t>(Optional) Pressure to which the sample is subject, in atmospheres (Units: atm)</t>
   </si>
   <si>
     <t>temperature</t>
@@ -2271,7 +2271,7 @@
     <t>bishomohopanol</t>
   </si>
   <si>
-    <t>(Optional) Concentration of bishomohopanol (Units: µg/g)</t>
+    <t>(Optional) Concentration of bishomohopanol (Units: µg/L)</t>
   </si>
   <si>
     <t>bromide</t>
@@ -2283,7 +2283,7 @@
     <t>calcium</t>
   </si>
   <si>
-    <t>(Optional) Concentration of calcium (Units: µmol/L)</t>
+    <t>(Optional) Concentration of calcium (Units: mg/L)</t>
   </si>
   <si>
     <t>carbon/nitrogen ratio</t>
@@ -2367,7 +2367,7 @@
     <t>magnesium</t>
   </si>
   <si>
-    <t>(Optional) Concentration of magnesium (Units: parts/million)</t>
+    <t>(Optional) Concentration of magnesium (Units: mg/L)</t>
   </si>
   <si>
     <t>n-alkanes</t>
@@ -2457,7 +2457,7 @@
     <t>primary production</t>
   </si>
   <si>
-    <t>(Optional) Measurement of primary production (Units: mg/m3/day)</t>
+    <t>(Optional) Measurement of primary production (Units: g/m2/day)</t>
   </si>
   <si>
     <t>redox potential</t>
@@ -2493,13 +2493,13 @@
     <t>sulfate</t>
   </si>
   <si>
-    <t>(Optional) Concentration of sulfate (Units: µmol/L)</t>
+    <t>(Optional) Concentration of sulfate (Units: mg/L)</t>
   </si>
   <si>
     <t>sulfide</t>
   </si>
   <si>
-    <t>(Optional) Concentration of sulfide (Units: µmol/L)</t>
+    <t>(Optional) Concentration of sulfide (Units: mg/L)</t>
   </si>
   <si>
     <t>suspended particulate matter</t>
@@ -2523,13 +2523,13 @@
     <t>total nitrogen content</t>
   </si>
   <si>
-    <t>(Optional) Total nitrogen content of the sample (Units: µmol/L)</t>
+    <t>(Optional) Total nitrogen content of the sample (Units: µg/L)</t>
   </si>
   <si>
     <t>total particulate carbon</t>
   </si>
   <si>
-    <t>(Optional) Total particulate carbon content (Units: µmol/L)</t>
+    <t>(Optional) Total particulate carbon content (Units: µg/L)</t>
   </si>
   <si>
     <t>total phosphorus</t>
@@ -2625,7 +2625,7 @@
     <t>sample volume or weight for DNA extraction</t>
   </si>
   <si>
-    <t>(Optional) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: ng)</t>
+    <t>(Optional) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: mL)</t>
   </si>
   <si>
     <t>nucleic acid extraction</t>
@@ -2691,7 +2691,7 @@
     <t>depth</t>
   </si>
   <si>
-    <t>(Mandatory) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: mm)</t>
+    <t>(Mandatory) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: m)</t>
   </si>
   <si>
     <t>chemical administration</t>
